--- a/Provider_Stress_Output/Summary_By_Method.xlsx
+++ b/Provider_Stress_Output/Summary_By_Method.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,100 +457,108 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>avg_distance_km</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total_assigned</t>
         </is>
       </c>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>edd</t>
         </is>
@@ -553,7 +601,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>greedy</t>
         </is>
@@ -596,7 +644,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>nearest</t>
         </is>
@@ -639,7 +687,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>round_robin</t>
         </is>

--- a/Provider_Stress_Output/Summary_By_Method.xlsx
+++ b/Provider_Stress_Output/Summary_By_Method.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,49 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -457,108 +417,100 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr"/>
+      <c r="B1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>avg_distance_km</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>avg_travel_hours</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
       </c>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>total_assigned</t>
         </is>
       </c>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>edd</t>
         </is>
@@ -573,13 +525,13 @@
         <v>3.75</v>
       </c>
       <c r="E4" t="n">
-        <v>11.87</v>
+        <v>0.51</v>
       </c>
       <c r="F4" t="n">
-        <v>9.460000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="G4" t="n">
-        <v>14.54</v>
+        <v>0.63</v>
       </c>
       <c r="H4" t="n">
         <v>32.57</v>
@@ -601,7 +553,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>greedy</t>
         </is>
@@ -616,13 +568,13 @@
         <v>3.75</v>
       </c>
       <c r="E5" t="n">
-        <v>11.8</v>
+        <v>0.51</v>
       </c>
       <c r="F5" t="n">
-        <v>9.23</v>
+        <v>0.4</v>
       </c>
       <c r="G5" t="n">
-        <v>14.77</v>
+        <v>0.64</v>
       </c>
       <c r="H5" t="n">
         <v>33</v>
@@ -644,7 +596,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>nearest</t>
         </is>
@@ -659,13 +611,13 @@
         <v>13.32</v>
       </c>
       <c r="E6" t="n">
-        <v>6.92</v>
+        <v>0.3</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>0.26</v>
       </c>
       <c r="G6" t="n">
-        <v>8.31</v>
+        <v>0.36</v>
       </c>
       <c r="H6" t="n">
         <v>47.71</v>
@@ -687,7 +639,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>round_robin</t>
         </is>
@@ -702,13 +654,13 @@
         <v>14.28</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>0.52</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>0.52</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>0.52</v>
       </c>
       <c r="H7" t="n">
         <v>67</v>

--- a/Provider_Stress_Output/Summary_By_Method.xlsx
+++ b/Provider_Stress_Output/Summary_By_Method.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,100 +457,108 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>avg_travel_hours</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total_assigned</t>
         </is>
       </c>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>edd</t>
         </is>
@@ -553,7 +601,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>greedy</t>
         </is>
@@ -596,7 +644,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>nearest</t>
         </is>
@@ -639,7 +687,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>round_robin</t>
         </is>
